--- a/hardware/variante_3ch/jlcpcb/CPL_JLCPCB.xlsx
+++ b/hardware/variante_3ch/jlcpcb/CPL_JLCPCB.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.000mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>131.000mm</t>
+          <t>188.500mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,12 +478,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>44.500mm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>140.500mm</t>
+          <t>198.000mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -505,12 +505,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.000mm</t>
+          <t>48.500mm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>140.500mm</t>
+          <t>198.000mm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.000mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>144.000mm</t>
+          <t>201.000mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -559,12 +559,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24.500mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>117.000mm</t>
+          <t>132.000mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.500mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>148.000mm</t>
+          <t>156.500mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13.500mm</t>
+          <t>16.500mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>156.000mm</t>
+          <t>164.000mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>51.500mm</t>
+          <t>54.500mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>148.500mm</t>
+          <t>156.500mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>40.500mm</t>
+          <t>43.500mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>156.000mm</t>
+          <t>164.000mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>58.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>141.000mm</t>
+          <t>136.000mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24.500mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>62.000mm</t>
+          <t>80.000mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14.500mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>93.000mm</t>
+          <t>104.500mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13.500mm</t>
+          <t>16.500mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>101.000mm</t>
+          <t>112.000mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>51.500mm</t>
+          <t>54.500mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>93.500mm</t>
+          <t>104.500mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>40.500mm</t>
+          <t>43.500mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>101.000mm</t>
+          <t>112.000mm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>58.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>86.000mm</t>
+          <t>84.000mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24.500mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>28.000mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14.500mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>38.000mm</t>
+          <t>52.500mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13.500mm</t>
+          <t>16.500mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>60.000mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>51.500mm</t>
+          <t>54.500mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>38.500mm</t>
+          <t>52.500mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>40.500mm</t>
+          <t>43.500mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>60.000mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>58.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>31.000mm</t>
+          <t>32.000mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>60.600mm</t>
+          <t>67.000mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>137.200mm</t>
+          <t>197.000mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>41.500mm</t>
+          <t>67.000mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>127.500mm</t>
+          <t>187.000mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>72.300mm</t>
+          <t>14.000mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>124.200mm</t>
+          <t>185.000mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>60.000mm</t>
+          <t>20.000mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>123.500mm</t>
+          <t>185.000mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>66.500mm</t>
+          <t>82.000mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>69.500mm</t>
+          <t>14.500mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24.500mm</t>
+          <t>27.500mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>163.500mm</t>
+          <t>171.500mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>51.500mm</t>
+          <t>54.500mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>161.000mm</t>
+          <t>169.000mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>69.000mm</t>
+          <t>76.000mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>150.000mm</t>
+          <t>145.000mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>65.500mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>145.000mm</t>
+          <t>140.000mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>73.000mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>132.500mm</t>
+          <t>170.000mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24.500mm</t>
+          <t>27.500mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>108.500mm</t>
+          <t>119.500mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>51.500mm</t>
+          <t>54.500mm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>106.000mm</t>
+          <t>117.000mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>69.000mm</t>
+          <t>76.000mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>95.000mm</t>
+          <t>93.000mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>65.500mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>90.000mm</t>
+          <t>88.000mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>73.000mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>77.500mm</t>
+          <t>118.000mm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>24.500mm</t>
+          <t>27.500mm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>53.500mm</t>
+          <t>67.500mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>51.500mm</t>
+          <t>54.500mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>51.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>69.000mm</t>
+          <t>76.000mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>40.000mm</t>
+          <t>41.000mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>65.500mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>35.000mm</t>
+          <t>36.000mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>73.000mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>22.500mm</t>
+          <t>66.000mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>72.500mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>139.000mm</t>
+          <t>134.000mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>72.500mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>84.000mm</t>
+          <t>82.000mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>72.500mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>30.000mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>31.000mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>137.500mm</t>
+          <t>194.000mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22.000mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>154.117mm</t>
+          <t>162.117mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>32.500mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>155.383mm</t>
+          <t>163.383mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22.000mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>99.117mm</t>
+          <t>110.117mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>32.500mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>100.383mm</t>
+          <t>111.383mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22.000mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>44.117mm</t>
+          <t>58.117mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>32.500mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>45.383mm</t>
+          <t>59.383mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4.000mm</t>
+          <t>49.500mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>121.000mm</t>
+          <t>188.000mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4.000mm</t>
+          <t>46.500mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>124.000mm</t>
+          <t>188.000mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14.000mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>134.000mm</t>
+          <t>192.000mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4.000mm</t>
+          <t>43.500mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>127.000mm</t>
+          <t>188.000mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>69.500mm</t>
+          <t>85.500mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>66.000mm</t>
+          <t>8.500mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>58.000mm</t>
+          <t>61.200mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>60.000mm</t>
+          <t>67.200mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>61.500mm</t>
+          <t>73.200mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>69.500mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21.000mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>128.500mm</t>
+          <t>143.500mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>27.000mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>130.000mm</t>
+          <t>145.000mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21.500mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>120.500mm</t>
+          <t>135.500mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26.000mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>113.500mm</t>
+          <t>128.500mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>148.000mm</t>
+          <t>156.500mm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>20.000mm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>151.500mm</t>
+          <t>159.500mm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10.000mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>151.500mm</t>
+          <t>163.000mm</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22.000mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>160.500mm</t>
+          <t>168.500mm</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>28.000mm</t>
+          <t>31.000mm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>160.500mm</t>
+          <t>168.500mm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>32.500mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>160.500mm</t>
+          <t>168.500mm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>36.500mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>151.500mm</t>
+          <t>159.500mm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>44.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>151.500mm</t>
+          <t>159.500mm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>46.500mm</t>
+          <t>49.500mm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>148.500mm</t>
+          <t>156.500mm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>49.000mm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>144.000mm</t>
+          <t>152.000mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>139.000mm</t>
+          <t>143.500mm</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>49.000mm</t>
+          <t>52.000mm</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>138.500mm</t>
+          <t>143.000mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>58.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>149.500mm</t>
+          <t>144.500mm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>72.500mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>145.000mm</t>
+          <t>140.000mm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>69.800mm</t>
+          <t>79.000mm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>127.400mm</t>
+          <t>166.800mm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>21.000mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>73.500mm</t>
+          <t>91.500mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>27.000mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>75.000mm</t>
+          <t>93.000mm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>21.500mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>65.500mm</t>
+          <t>83.500mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>26.000mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>76.500mm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>93.000mm</t>
+          <t>104.500mm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>20.000mm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>96.500mm</t>
+          <t>107.500mm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>10.000mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>96.500mm</t>
+          <t>111.000mm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>22.000mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>105.500mm</t>
+          <t>116.500mm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>28.000mm</t>
+          <t>31.000mm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>105.500mm</t>
+          <t>116.500mm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>32.500mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>105.500mm</t>
+          <t>116.500mm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>36.500mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>96.500mm</t>
+          <t>107.500mm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>44.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>96.500mm</t>
+          <t>107.500mm</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>46.500mm</t>
+          <t>49.500mm</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>93.500mm</t>
+          <t>104.500mm</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>49.000mm</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>89.000mm</t>
+          <t>100.000mm</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>84.000mm</t>
+          <t>91.500mm</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>49.000mm</t>
+          <t>52.000mm</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>83.500mm</t>
+          <t>91.000mm</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>58.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>94.500mm</t>
+          <t>92.500mm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>72.500mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>90.000mm</t>
+          <t>88.000mm</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>69.800mm</t>
+          <t>79.000mm</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>72.400mm</t>
+          <t>114.800mm</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>21.000mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>18.500mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>27.000mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>41.000mm</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21.500mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>31.500mm</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>26.000mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3.500mm</t>
+          <t>24.500mm</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>38.000mm</t>
+          <t>52.500mm</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>20.000mm</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>41.500mm</t>
+          <t>55.500mm</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>10.000mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>41.500mm</t>
+          <t>59.000mm</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3286,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>22.000mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>50.500mm</t>
+          <t>64.500mm</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>28.000mm</t>
+          <t>31.000mm</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>50.500mm</t>
+          <t>64.500mm</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>32.500mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>50.500mm</t>
+          <t>64.500mm</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>36.500mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>41.500mm</t>
+          <t>55.500mm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>44.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>41.500mm</t>
+          <t>55.500mm</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>46.500mm</t>
+          <t>49.500mm</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>38.500mm</t>
+          <t>52.500mm</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>49.000mm</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>34.000mm</t>
+          <t>48.000mm</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>49.000mm</t>
+          <t>52.000mm</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>28.500mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>58.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>40.500mm</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>72.500mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>35.000mm</t>
+          <t>36.000mm</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>69.800mm</t>
+          <t>79.000mm</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>17.400mm</t>
+          <t>62.800mm</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>66.000mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>117.925mm</t>
+          <t>191.425mm</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>64.000mm</t>
+          <t>82.000mm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>9.500mm</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>64.000mm</t>
+          <t>71.000mm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>145.000mm</t>
+          <t>140.000mm</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>68.190mm</t>
+          <t>73.190mm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>132.240mm</t>
+          <t>165.240mm</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>64.000mm</t>
+          <t>71.000mm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>90.000mm</t>
+          <t>88.000mm</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>68.190mm</t>
+          <t>73.190mm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>77.240mm</t>
+          <t>113.240mm</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>64.000mm</t>
+          <t>71.000mm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>35.000mm</t>
+          <t>36.000mm</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>68.190mm</t>
+          <t>73.190mm</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>22.240mm</t>
+          <t>61.240mm</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>33.000mm</t>
+          <t>19.000mm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>115.500mm</t>
+          <t>130.500mm</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>43.000mm</t>
+          <t>46.000mm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>134.000mm</t>
+          <t>138.500mm</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>33.000mm</t>
+          <t>19.000mm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>60.500mm</t>
+          <t>78.500mm</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>43.000mm</t>
+          <t>46.000mm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>79.000mm</t>
+          <t>86.500mm</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>33.000mm</t>
+          <t>19.000mm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>5.500mm</t>
+          <t>26.500mm</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>43.000mm</t>
+          <t>46.000mm</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>24.000mm</t>
+          <t>34.500mm</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">

--- a/hardware/variante_3ch/jlcpcb/CPL_JLCPCB.xlsx
+++ b/hardware/variante_3ch/jlcpcb/CPL_JLCPCB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,17 +554,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>57.000mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>132.000mm</t>
+          <t>189.500mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,24 +574,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>156.500mm</t>
+          <t>132.000mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C107</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16.500mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>164.000mm</t>
+          <t>156.500mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C109</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>54.500mm</t>
+          <t>16.500mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>156.500mm</t>
+          <t>164.000mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -662,17 +662,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C111</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>43.500mm</t>
+          <t>54.500mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>164.000mm</t>
+          <t>156.500mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -689,17 +689,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C121</t>
+          <t>C111</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>43.500mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>136.000mm</t>
+          <t>164.000mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,24 +709,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C204</t>
+          <t>C121</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>80.000mm</t>
+          <t>136.000mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,24 +736,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C206</t>
+          <t>C150</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104.500mm</t>
+          <t>142.500mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -770,17 +770,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C207</t>
+          <t>C204</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16.500mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>112.000mm</t>
+          <t>80.000mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -797,12 +797,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C209</t>
+          <t>C206</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>54.500mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -817,19 +817,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C211</t>
+          <t>C207</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>43.500mm</t>
+          <t>16.500mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,17 +851,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C221</t>
+          <t>C209</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>54.500mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>84.000mm</t>
+          <t>104.500mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -871,24 +871,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C304</t>
+          <t>C211</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>43.500mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>28.000mm</t>
+          <t>112.000mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -905,17 +905,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C306</t>
+          <t>C221</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>52.500mm</t>
+          <t>84.000mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -932,17 +932,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C307</t>
+          <t>C250</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16.500mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>60.000mm</t>
+          <t>90.500mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -952,24 +952,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C309</t>
+          <t>C304</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>54.500mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>52.500mm</t>
+          <t>28.000mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -986,17 +986,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C311</t>
+          <t>C306</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>43.500mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>60.000mm</t>
+          <t>52.500mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1006,24 +1006,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C321</t>
+          <t>C307</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>16.500mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>32.000mm</t>
+          <t>60.000mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1033,24 +1033,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CF4</t>
+          <t>C309</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>67.000mm</t>
+          <t>54.500mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>197.000mm</t>
+          <t>52.500mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1060,24 +1060,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CF7</t>
+          <t>C311</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>67.000mm</t>
+          <t>43.500mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>187.000mm</t>
+          <t>60.000mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1087,24 +1087,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CF8</t>
+          <t>C321</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>185.000mm</t>
+          <t>32.000mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CF9</t>
+          <t>C350</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>185.000mm</t>
+          <t>38.500mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1141,24 +1141,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CF11</t>
+          <t>CF4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>82.000mm</t>
+          <t>67.000mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14.500mm</t>
+          <t>197.000mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1168,24 +1168,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CF101</t>
+          <t>CF7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27.500mm</t>
+          <t>67.000mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>171.500mm</t>
+          <t>187.000mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1195,24 +1195,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CF102</t>
+          <t>CF8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>54.500mm</t>
+          <t>14.000mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>169.000mm</t>
+          <t>185.000mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1229,17 +1229,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CF105</t>
+          <t>CF9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>76.000mm</t>
+          <t>20.000mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>145.000mm</t>
+          <t>185.000mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1256,17 +1256,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CF106</t>
+          <t>CF11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>65.500mm</t>
+          <t>82.000mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>140.000mm</t>
+          <t>14.500mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1276,24 +1276,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CF110</t>
+          <t>CF12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>73.000mm</t>
+          <t>77.000mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>170.000mm</t>
+          <t>201.000mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CF201</t>
+          <t>CF101</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>119.500mm</t>
+          <t>171.500mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CF202</t>
+          <t>CF102</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>117.000mm</t>
+          <t>169.000mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CF205</t>
+          <t>CF105</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>93.000mm</t>
+          <t>145.000mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CF206</t>
+          <t>CF106</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>88.000mm</t>
+          <t>140.000mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CF210</t>
+          <t>CF110</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>118.000mm</t>
+          <t>170.000mm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1445,7 +1445,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CF301</t>
+          <t>CF201</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>67.500mm</t>
+          <t>119.500mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1472,7 +1472,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CF302</t>
+          <t>CF202</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>117.000mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CF305</t>
+          <t>CF205</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>41.000mm</t>
+          <t>93.000mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1526,7 +1526,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CF306</t>
+          <t>CF206</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>88.000mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CF310</t>
+          <t>CF210</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>66.000mm</t>
+          <t>118.000mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1580,17 +1580,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>CF301</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>27.500mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>134.000mm</t>
+          <t>67.500mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1600,24 +1600,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>D203</t>
+          <t>CF302</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>54.500mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>82.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1627,24 +1627,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D303</t>
+          <t>CF305</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>76.000mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>30.000mm</t>
+          <t>41.000mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1654,24 +1654,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>CF306</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>31.000mm</t>
+          <t>65.500mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>194.000mm</t>
+          <t>36.000mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1688,17 +1688,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Q101</t>
+          <t>CF310</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>73.000mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>162.117mm</t>
+          <t>66.000mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1715,17 +1715,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Q102</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>163.383mm</t>
+          <t>134.000mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1735,24 +1735,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Q201</t>
+          <t>D203</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>110.117mm</t>
+          <t>82.000mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1762,24 +1762,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Q202</t>
+          <t>D303</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>111.383mm</t>
+          <t>30.000mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1789,24 +1789,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Q301</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>31.000mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>58.117mm</t>
+          <t>194.000mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Q302</t>
+          <t>Q101</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>59.383mm</t>
+          <t>162.117mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1843,24 +1843,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Q102</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>49.500mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>188.000mm</t>
+          <t>163.383mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1870,24 +1870,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Q201</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>46.500mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>188.000mm</t>
+          <t>110.117mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1897,24 +1897,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Q202</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>192.000mm</t>
+          <t>111.383mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1924,24 +1924,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>Q301</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>43.500mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>188.000mm</t>
+          <t>58.117mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1951,24 +1951,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>Q302</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>85.500mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.500mm</t>
+          <t>59.383mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1978,24 +1978,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>61.200mm</t>
+          <t>49.500mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>188.000mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2005,24 +2005,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>67.200mm</t>
+          <t>46.500mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>188.000mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2032,24 +2032,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>73.200mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>192.000mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>R104</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>43.500mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>143.500mm</t>
+          <t>188.000mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2093,17 +2093,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R105</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>85.500mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>145.000mm</t>
+          <t>8.500mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2113,24 +2113,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R106</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7.500mm</t>
+          <t>61.200mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>135.500mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2140,24 +2140,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R107</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>67.200mm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>128.500mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2167,24 +2167,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R108</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8.000mm</t>
+          <t>73.200mm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>156.500mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2194,24 +2194,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>R109</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>57.000mm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>159.500mm</t>
+          <t>200.000mm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2228,17 +2228,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R110</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11.500mm</t>
+          <t>57.000mm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>163.000mm</t>
+          <t>194.500mm</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2248,24 +2248,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R111</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>87.300mm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>168.500mm</t>
+          <t>195.000mm</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2282,17 +2282,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>R112</t>
+          <t>R43</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>31.000mm</t>
+          <t>87.300mm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>168.500mm</t>
+          <t>192.000mm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2302,24 +2302,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>R113</t>
+          <t>R104</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>168.500mm</t>
+          <t>143.500mm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2336,17 +2336,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>R114</t>
+          <t>R105</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>159.500mm</t>
+          <t>145.000mm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2356,24 +2356,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>R115</t>
+          <t>R106</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>159.500mm</t>
+          <t>135.500mm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2390,17 +2390,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>R116</t>
+          <t>R107</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>49.500mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>156.500mm</t>
+          <t>128.500mm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2410,24 +2410,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>R117</t>
+          <t>R108</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>49.000mm</t>
+          <t>8.000mm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>152.000mm</t>
+          <t>156.500mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2437,24 +2437,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>R118</t>
+          <t>R109</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>20.000mm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>143.500mm</t>
+          <t>159.500mm</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2464,24 +2464,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>R119</t>
+          <t>R110</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>52.000mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>143.000mm</t>
+          <t>163.000mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>R120</t>
+          <t>R111</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>144.500mm</t>
+          <t>168.500mm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2525,17 +2525,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>R121</t>
+          <t>R112</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>31.000mm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>140.000mm</t>
+          <t>168.500mm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2552,17 +2552,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>R123</t>
+          <t>R113</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>79.000mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>166.800mm</t>
+          <t>168.500mm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2572,24 +2572,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>R204</t>
+          <t>R114</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>91.500mm</t>
+          <t>159.500mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2606,17 +2606,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>R205</t>
+          <t>R115</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>93.000mm</t>
+          <t>159.500mm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2626,24 +2626,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>R206</t>
+          <t>R116</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7.500mm</t>
+          <t>49.500mm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>83.500mm</t>
+          <t>156.500mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2660,17 +2660,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>R207</t>
+          <t>R117</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>49.000mm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>76.500mm</t>
+          <t>152.000mm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>R208</t>
+          <t>R118</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>8.000mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>104.500mm</t>
+          <t>143.500mm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2707,24 +2707,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>R209</t>
+          <t>R119</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>52.000mm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>107.500mm</t>
+          <t>143.000mm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2734,24 +2734,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>R210</t>
+          <t>R120</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11.500mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>111.000mm</t>
+          <t>144.500mm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>R211</t>
+          <t>R121</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>116.500mm</t>
+          <t>140.000mm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2788,24 +2788,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>R212</t>
+          <t>R123</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>31.000mm</t>
+          <t>79.000mm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>116.500mm</t>
+          <t>166.800mm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2815,24 +2815,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>R213</t>
+          <t>R150</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>21.000mm</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>116.500mm</t>
+          <t>145.000mm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2842,24 +2842,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>R214</t>
+          <t>R151</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>25.500mm</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>107.500mm</t>
+          <t>142.500mm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2876,17 +2876,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>R215</t>
+          <t>R204</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>107.500mm</t>
+          <t>91.500mm</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2903,17 +2903,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>R216</t>
+          <t>R205</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>49.500mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>104.500mm</t>
+          <t>93.000mm</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2923,24 +2923,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>R217</t>
+          <t>R206</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>49.000mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>100.000mm</t>
+          <t>83.500mm</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2950,24 +2950,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>R218</t>
+          <t>R207</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>91.500mm</t>
+          <t>76.500mm</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2984,17 +2984,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>R219</t>
+          <t>R208</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>52.000mm</t>
+          <t>8.000mm</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>91.000mm</t>
+          <t>104.500mm</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3004,24 +3004,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>R220</t>
+          <t>R209</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>20.000mm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>92.500mm</t>
+          <t>107.500mm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3031,24 +3031,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>R221</t>
+          <t>R210</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>88.000mm</t>
+          <t>111.000mm</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3058,24 +3058,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>R223</t>
+          <t>R211</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>79.000mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>114.800mm</t>
+          <t>116.500mm</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3092,17 +3092,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>R304</t>
+          <t>R212</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>31.000mm</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>116.500mm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3119,17 +3119,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>R305</t>
+          <t>R213</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>41.000mm</t>
+          <t>116.500mm</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3139,24 +3139,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>R306</t>
+          <t>R214</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7.500mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>31.500mm</t>
+          <t>107.500mm</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3173,17 +3173,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>R307</t>
+          <t>R215</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>24.500mm</t>
+          <t>107.500mm</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3193,24 +3193,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>R308</t>
+          <t>R216</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8.000mm</t>
+          <t>49.500mm</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>52.500mm</t>
+          <t>104.500mm</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3227,17 +3227,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>R309</t>
+          <t>R217</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>49.000mm</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>55.500mm</t>
+          <t>100.000mm</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3247,24 +3247,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>R310</t>
+          <t>R218</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>11.500mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>59.000mm</t>
+          <t>91.500mm</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3274,24 +3274,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>R311</t>
+          <t>R219</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>52.000mm</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>91.000mm</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3308,17 +3308,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>R312</t>
+          <t>R220</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>31.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>92.500mm</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3328,24 +3328,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>R313</t>
+          <t>R221</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>88.000mm</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3362,17 +3362,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>R314</t>
+          <t>R223</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>79.000mm</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>55.500mm</t>
+          <t>114.800mm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3382,24 +3382,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>R315</t>
+          <t>R250</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>21.000mm</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>55.500mm</t>
+          <t>93.000mm</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3409,24 +3409,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>R316</t>
+          <t>R251</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>49.500mm</t>
+          <t>25.500mm</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>52.500mm</t>
+          <t>90.500mm</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3443,17 +3443,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>R317</t>
+          <t>R304</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>49.000mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>48.000mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3463,24 +3463,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>R318</t>
+          <t>R305</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>41.000mm</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3497,17 +3497,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>R319</t>
+          <t>R306</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>52.000mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>31.500mm</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3517,24 +3517,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>R320</t>
+          <t>R307</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>40.500mm</t>
+          <t>24.500mm</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3551,17 +3551,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>R321</t>
+          <t>R308</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>8.000mm</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>52.500mm</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3578,17 +3578,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>R323</t>
+          <t>R309</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>79.000mm</t>
+          <t>20.000mm</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>62.800mm</t>
+          <t>55.500mm</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3598,24 +3598,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>R310</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>191.425mm</t>
+          <t>59.000mm</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3625,24 +3625,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>R311</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>82.000mm</t>
+          <t>25.000mm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>9.500mm</t>
+          <t>64.500mm</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3659,17 +3659,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>U102</t>
+          <t>R312</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>71.000mm</t>
+          <t>31.000mm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>140.000mm</t>
+          <t>64.500mm</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3679,24 +3679,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>U109</t>
+          <t>R313</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>73.190mm</t>
+          <t>35.500mm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>165.240mm</t>
+          <t>64.500mm</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>U202</t>
+          <t>R314</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>71.000mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>88.000mm</t>
+          <t>55.500mm</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3733,24 +3733,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>U209</t>
+          <t>R315</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>73.190mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>113.240mm</t>
+          <t>55.500mm</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3760,24 +3760,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>U302</t>
+          <t>R316</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>71.000mm</t>
+          <t>49.500mm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>52.500mm</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3787,24 +3787,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>U309</t>
+          <t>R317</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>73.190mm</t>
+          <t>49.000mm</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>61.240mm</t>
+          <t>48.000mm</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3821,17 +3821,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>V101</t>
+          <t>R318</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>19.000mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>130.500mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3848,17 +3848,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>V102</t>
+          <t>R319</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>52.000mm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>138.500mm</t>
+          <t>39.000mm</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3875,17 +3875,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>V201</t>
+          <t>R320</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>19.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>78.500mm</t>
+          <t>40.500mm</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3902,17 +3902,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>V202</t>
+          <t>R321</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>79.500mm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>86.500mm</t>
+          <t>36.000mm</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3922,24 +3922,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>V301</t>
+          <t>R323</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>19.000mm</t>
+          <t>79.000mm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>26.500mm</t>
+          <t>62.800mm</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3956,25 +3956,457 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>R350</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>21.000mm</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>41.000mm</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>R351</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>25.500mm</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>38.500mm</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>17.000mm</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>191.425mm</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>82.000mm</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>9.500mm</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>79.500mm</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>194.000mm</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>U102</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>71.000mm</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>140.000mm</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>U109</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>73.190mm</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>165.240mm</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>U202</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>71.000mm</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>88.000mm</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>U209</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>73.190mm</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>113.240mm</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>U302</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>71.000mm</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>36.000mm</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>U309</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>73.190mm</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>61.240mm</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>V101</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>19.000mm</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>130.500mm</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>V102</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>46.000mm</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>138.500mm</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>V201</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>19.000mm</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>78.500mm</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>V202</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>46.000mm</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>86.500mm</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>V301</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>19.000mm</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>26.500mm</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>V302</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>46.000mm</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>34.500mm</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/hardware/variante_3ch/jlcpcb/CPL_JLCPCB.xlsx
+++ b/hardware/variante_3ch/jlcpcb/CPL_JLCPCB.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>47.255mm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>188.500mm</t>
+          <t>198.500mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,12 +478,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>44.500mm</t>
+          <t>52.755mm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>198.000mm</t>
+          <t>208.000mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -505,12 +505,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48.500mm</t>
+          <t>56.755mm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>198.000mm</t>
+          <t>208.000mm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>37.255mm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>201.000mm</t>
+          <t>211.000mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -559,12 +559,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>57.000mm</t>
+          <t>65.255mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>189.500mm</t>
+          <t>199.500mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>132.000mm</t>
+          <t>142.000mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>156.500mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16.500mm</t>
+          <t>18.405mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>164.000mm</t>
+          <t>174.000mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>54.500mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>156.500mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>43.500mm</t>
+          <t>47.310mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>164.000mm</t>
+          <t>174.000mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>136.000mm</t>
+          <t>146.000mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>142.500mm</t>
+          <t>152.500mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>80.000mm</t>
+          <t>88.000mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104.500mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16.500mm</t>
+          <t>18.405mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>112.000mm</t>
+          <t>120.000mm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>54.500mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104.500mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>43.500mm</t>
+          <t>47.310mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>112.000mm</t>
+          <t>120.000mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>84.000mm</t>
+          <t>92.000mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>90.500mm</t>
+          <t>98.500mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>28.000mm</t>
+          <t>34.000mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>52.500mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16.500mm</t>
+          <t>18.405mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>60.000mm</t>
+          <t>66.000mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>54.500mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>52.500mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>43.500mm</t>
+          <t>47.310mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>60.000mm</t>
+          <t>66.000mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>32.000mm</t>
+          <t>38.000mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>38.500mm</t>
+          <t>44.500mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>67.000mm</t>
+          <t>77.795mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>197.000mm</t>
+          <t>207.000mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>67.000mm</t>
+          <t>77.795mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>187.000mm</t>
+          <t>197.000mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14.000mm</t>
+          <t>20.350mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>185.000mm</t>
+          <t>195.000mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>26.350mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>185.000mm</t>
+          <t>195.000mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>82.000mm</t>
+          <t>88.350mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14.500mm</t>
+          <t>18.500mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>77.000mm</t>
+          <t>89.535mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>201.000mm</t>
+          <t>193.000mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>27.500mm</t>
+          <t>29.405mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>171.500mm</t>
+          <t>181.500mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>54.500mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>169.000mm</t>
+          <t>179.000mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>76.000mm</t>
+          <t>82.350mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>145.000mm</t>
+          <t>155.000mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>65.500mm</t>
+          <t>71.850mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>140.000mm</t>
+          <t>150.000mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>73.000mm</t>
+          <t>79.350mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>170.000mm</t>
+          <t>180.000mm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>27.500mm</t>
+          <t>29.405mm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>119.500mm</t>
+          <t>127.500mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>54.500mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>117.000mm</t>
+          <t>125.000mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>76.000mm</t>
+          <t>82.350mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>93.000mm</t>
+          <t>101.000mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>65.500mm</t>
+          <t>71.850mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>88.000mm</t>
+          <t>96.000mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>73.000mm</t>
+          <t>79.350mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>118.000mm</t>
+          <t>126.000mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>27.500mm</t>
+          <t>29.405mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>67.500mm</t>
+          <t>73.500mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>54.500mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>71.000mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>76.000mm</t>
+          <t>82.350mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>41.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>65.500mm</t>
+          <t>71.850mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>42.000mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>73.000mm</t>
+          <t>79.350mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>66.000mm</t>
+          <t>72.000mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>134.000mm</t>
+          <t>144.000mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>82.000mm</t>
+          <t>90.000mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>30.000mm</t>
+          <t>36.000mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>31.000mm</t>
+          <t>39.255mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>194.000mm</t>
+          <t>204.000mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>162.117mm</t>
+          <t>172.117mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>163.383mm</t>
+          <t>173.383mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>110.117mm</t>
+          <t>118.117mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>111.383mm</t>
+          <t>119.383mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.117mm</t>
+          <t>64.117mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1963,12 +1963,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>59.383mm</t>
+          <t>65.383mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>49.500mm</t>
+          <t>57.755mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>188.000mm</t>
+          <t>198.000mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>46.500mm</t>
+          <t>54.755mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>188.000mm</t>
+          <t>198.000mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>47.255mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>192.000mm</t>
+          <t>202.000mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>43.500mm</t>
+          <t>51.755mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>188.000mm</t>
+          <t>198.000mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>85.500mm</t>
+          <t>91.850mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>8.500mm</t>
+          <t>12.500mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>61.200mm</t>
+          <t>67.550mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>67.200mm</t>
+          <t>73.550mm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>73.200mm</t>
+          <t>79.550mm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>57.000mm</t>
+          <t>65.255mm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>200.000mm</t>
+          <t>210.000mm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>57.000mm</t>
+          <t>65.255mm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>194.500mm</t>
+          <t>204.500mm</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>87.300mm</t>
+          <t>96.600mm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>195.000mm</t>
+          <t>200.000mm</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>87.300mm</t>
+          <t>96.600mm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>192.000mm</t>
+          <t>197.000mm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>143.500mm</t>
+          <t>153.500mm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>145.000mm</t>
+          <t>155.000mm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>135.500mm</t>
+          <t>145.500mm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>128.500mm</t>
+          <t>138.500mm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>156.500mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>21.905mm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>159.500mm</t>
+          <t>169.500mm</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>163.000mm</t>
+          <t>173.000mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>168.500mm</t>
+          <t>178.500mm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>31.000mm</t>
+          <t>32.905mm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>168.500mm</t>
+          <t>178.500mm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>168.500mm</t>
+          <t>178.500mm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>41.405mm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>159.500mm</t>
+          <t>169.500mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>50.810mm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>159.500mm</t>
+          <t>169.500mm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>49.500mm</t>
+          <t>53.310mm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>156.500mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>49.000mm</t>
+          <t>52.810mm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>152.000mm</t>
+          <t>162.000mm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>42.810mm</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>143.500mm</t>
+          <t>153.500mm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>52.000mm</t>
+          <t>55.810mm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>143.000mm</t>
+          <t>153.000mm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>144.500mm</t>
+          <t>154.500mm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>140.000mm</t>
+          <t>150.000mm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>79.000mm</t>
+          <t>85.350mm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>166.800mm</t>
+          <t>176.800mm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>145.000mm</t>
+          <t>155.000mm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>142.500mm</t>
+          <t>152.500mm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>91.500mm</t>
+          <t>99.500mm</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>93.000mm</t>
+          <t>101.000mm</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>83.500mm</t>
+          <t>91.500mm</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>76.500mm</t>
+          <t>84.500mm</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>104.500mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>21.905mm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>107.500mm</t>
+          <t>115.500mm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>111.000mm</t>
+          <t>119.000mm</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>116.500mm</t>
+          <t>124.500mm</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>31.000mm</t>
+          <t>32.905mm</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>116.500mm</t>
+          <t>124.500mm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>116.500mm</t>
+          <t>124.500mm</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>41.405mm</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>107.500mm</t>
+          <t>115.500mm</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>50.810mm</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>107.500mm</t>
+          <t>115.500mm</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>49.500mm</t>
+          <t>53.310mm</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>104.500mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>49.000mm</t>
+          <t>52.810mm</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>100.000mm</t>
+          <t>108.000mm</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>42.810mm</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>91.500mm</t>
+          <t>99.500mm</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>52.000mm</t>
+          <t>55.810mm</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>91.000mm</t>
+          <t>99.000mm</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>92.500mm</t>
+          <t>100.500mm</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>88.000mm</t>
+          <t>96.000mm</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>79.000mm</t>
+          <t>85.350mm</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>114.800mm</t>
+          <t>122.800mm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>93.000mm</t>
+          <t>101.000mm</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>90.500mm</t>
+          <t>98.500mm</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>45.500mm</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>41.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>31.500mm</t>
+          <t>37.500mm</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>24.500mm</t>
+          <t>30.500mm</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>52.500mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>21.905mm</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>55.500mm</t>
+          <t>61.500mm</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>59.000mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>25.000mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>70.500mm</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>31.000mm</t>
+          <t>32.905mm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>70.500mm</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>35.500mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>64.500mm</t>
+          <t>70.500mm</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>41.405mm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>55.500mm</t>
+          <t>61.500mm</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>50.810mm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>55.500mm</t>
+          <t>61.500mm</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>49.500mm</t>
+          <t>53.310mm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>52.500mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>49.000mm</t>
+          <t>52.810mm</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>48.000mm</t>
+          <t>54.000mm</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>42.810mm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>45.500mm</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>52.000mm</t>
+          <t>55.810mm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>39.000mm</t>
+          <t>45.000mm</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>40.500mm</t>
+          <t>46.500mm</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>42.000mm</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>79.000mm</t>
+          <t>85.350mm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>62.800mm</t>
+          <t>68.800mm</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>41.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>38.500mm</t>
+          <t>44.500mm</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4015,12 +4015,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>23.350mm</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>191.425mm</t>
+          <t>201.425mm</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>82.000mm</t>
+          <t>88.350mm</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>9.500mm</t>
+          <t>13.500mm</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>79.500mm</t>
+          <t>89.535mm</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>194.000mm</t>
+          <t>199.500mm</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>71.000mm</t>
+          <t>77.350mm</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>140.000mm</t>
+          <t>150.000mm</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>73.190mm</t>
+          <t>79.540mm</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>165.240mm</t>
+          <t>175.240mm</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>71.000mm</t>
+          <t>77.350mm</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>88.000mm</t>
+          <t>96.000mm</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>73.190mm</t>
+          <t>79.540mm</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>113.240mm</t>
+          <t>121.240mm</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>71.000mm</t>
+          <t>77.350mm</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>42.000mm</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>73.190mm</t>
+          <t>79.540mm</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>61.240mm</t>
+          <t>67.240mm</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>130.500mm</t>
+          <t>140.500mm</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>49.810mm</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>138.500mm</t>
+          <t>148.500mm</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>78.500mm</t>
+          <t>86.500mm</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>49.810mm</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>86.500mm</t>
+          <t>94.500mm</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>26.500mm</t>
+          <t>32.500mm</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>49.810mm</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>34.500mm</t>
+          <t>40.500mm</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">

--- a/hardware/variante_3ch/jlcpcb/CPL_JLCPCB.xlsx
+++ b/hardware/variante_3ch/jlcpcb/CPL_JLCPCB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>198.500mm</t>
+          <t>207.390mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>208.000mm</t>
+          <t>216.890mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>208.000mm</t>
+          <t>216.890mm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>211.000mm</t>
+          <t>219.890mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>199.500mm</t>
+          <t>208.390mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -581,17 +581,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>90.170mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>142.000mm</t>
+          <t>194.390mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>166.500mm</t>
+          <t>142.000mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C107</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18.405mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>174.000mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,24 +655,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C109</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>58.310mm</t>
+          <t>18.405mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>166.500mm</t>
+          <t>174.000mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -689,17 +689,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C111</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>47.310mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>174.000mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -716,17 +716,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C121</t>
+          <t>C111</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>46.040mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>146.000mm</t>
+          <t>174.000mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,24 +736,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C150</t>
+          <t>C121</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>152.500mm</t>
+          <t>146.000mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -770,17 +770,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C204</t>
+          <t>C150</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>88.000mm</t>
+          <t>152.500mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,24 +790,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C206</t>
+          <t>C152</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>50.165mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>112.500mm</t>
+          <t>173.500mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -824,17 +824,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C207</t>
+          <t>C204</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18.405mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>120.000mm</t>
+          <t>88.000mm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C209</t>
+          <t>C206</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>58.310mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -871,19 +871,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C211</t>
+          <t>C207</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>47.310mm</t>
+          <t>18.405mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,17 +905,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C221</t>
+          <t>C209</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>92.000mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -925,24 +925,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C250</t>
+          <t>C211</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>46.040mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>98.500mm</t>
+          <t>120.000mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -952,24 +952,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C304</t>
+          <t>C221</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>34.000mm</t>
+          <t>92.000mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -979,24 +979,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C306</t>
+          <t>C250</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>98.500mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1013,17 +1013,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C307</t>
+          <t>C252</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18.405mm</t>
+          <t>50.165mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>66.000mm</t>
+          <t>119.500mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1033,24 +1033,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C309</t>
+          <t>C304</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>58.310mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>34.000mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1067,17 +1067,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C311</t>
+          <t>C306</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>47.310mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>66.000mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1087,24 +1087,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C321</t>
+          <t>C307</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>18.405mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>38.000mm</t>
+          <t>66.000mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C350</t>
+          <t>C309</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>44.500mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1141,24 +1141,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CF4</t>
+          <t>C311</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>77.795mm</t>
+          <t>46.040mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>207.000mm</t>
+          <t>66.000mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1168,24 +1168,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CF7</t>
+          <t>C321</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>77.795mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>197.000mm</t>
+          <t>38.000mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1202,17 +1202,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CF8</t>
+          <t>C350</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20.350mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>195.000mm</t>
+          <t>44.500mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1222,24 +1222,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CF9</t>
+          <t>C352</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>26.350mm</t>
+          <t>50.165mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>195.000mm</t>
+          <t>65.500mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1249,24 +1249,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CF11</t>
+          <t>CF4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>88.350mm</t>
+          <t>75.890mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18.500mm</t>
+          <t>215.890mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1276,24 +1276,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CF12</t>
+          <t>CF7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>89.535mm</t>
+          <t>75.890mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>193.000mm</t>
+          <t>205.890mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1303,24 +1303,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CF101</t>
+          <t>CF8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>29.405mm</t>
+          <t>20.350mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>181.500mm</t>
+          <t>203.890mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CF102</t>
+          <t>CF9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>58.310mm</t>
+          <t>26.350mm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>179.000mm</t>
+          <t>203.890mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1364,17 +1364,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CF105</t>
+          <t>CF11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>82.350mm</t>
+          <t>88.350mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>155.000mm</t>
+          <t>18.500mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1391,17 +1391,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CF106</t>
+          <t>CF12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>71.850mm</t>
+          <t>86.360mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>150.000mm</t>
+          <t>201.890mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1411,24 +1411,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CF110</t>
+          <t>CF13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>79.350mm</t>
+          <t>93.980mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>180.000mm</t>
+          <t>201.890mm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1445,7 +1445,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CF201</t>
+          <t>CF101</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>127.500mm</t>
+          <t>181.500mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1472,7 +1472,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CF202</t>
+          <t>CF102</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>125.000mm</t>
+          <t>179.000mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CF205</t>
+          <t>CF105</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>101.000mm</t>
+          <t>155.000mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1526,7 +1526,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CF206</t>
+          <t>CF106</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>96.000mm</t>
+          <t>150.000mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CF210</t>
+          <t>CF110</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>126.000mm</t>
+          <t>180.000mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1580,7 +1580,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CF301</t>
+          <t>CF201</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>73.500mm</t>
+          <t>127.500mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CF302</t>
+          <t>CF202</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>71.000mm</t>
+          <t>125.000mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CF305</t>
+          <t>CF205</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>101.000mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CF306</t>
+          <t>CF206</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>42.000mm</t>
+          <t>96.000mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1688,7 +1688,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CF310</t>
+          <t>CF210</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>72.000mm</t>
+          <t>126.000mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1715,17 +1715,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>CF301</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>29.405mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>144.000mm</t>
+          <t>73.500mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1735,24 +1735,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>D203</t>
+          <t>CF302</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>90.000mm</t>
+          <t>71.000mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1762,24 +1762,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>D303</t>
+          <t>CF305</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>82.350mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1789,24 +1789,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>CF306</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>39.255mm</t>
+          <t>71.850mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>204.000mm</t>
+          <t>42.000mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1823,17 +1823,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Q101</t>
+          <t>CF310</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>79.350mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>172.117mm</t>
+          <t>72.000mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1850,17 +1850,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Q102</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>173.383mm</t>
+          <t>144.000mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1870,24 +1870,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Q201</t>
+          <t>D203</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>118.117mm</t>
+          <t>90.000mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1897,24 +1897,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Q202</t>
+          <t>D303</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>119.383mm</t>
+          <t>36.000mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1924,24 +1924,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Q301</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>39.255mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.117mm</t>
+          <t>212.890mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1951,24 +1951,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Q302</t>
+          <t>Q101</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>65.383mm</t>
+          <t>172.117mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1978,24 +1978,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Q102</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>57.755mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>198.000mm</t>
+          <t>173.383mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2005,24 +2005,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Q201</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>54.755mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>198.000mm</t>
+          <t>118.117mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2032,24 +2032,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Q202</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>47.255mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>202.000mm</t>
+          <t>119.383mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>Q301</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>51.755mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>198.000mm</t>
+          <t>64.117mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2086,24 +2086,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>Q302</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>91.850mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>12.500mm</t>
+          <t>65.383mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2113,24 +2113,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>67.550mm</t>
+          <t>57.755mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>206.890mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2140,24 +2140,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>73.550mm</t>
+          <t>54.755mm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>206.890mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2167,24 +2167,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>79.550mm</t>
+          <t>47.255mm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>210.890mm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2194,24 +2194,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>65.255mm</t>
+          <t>51.755mm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>210.000mm</t>
+          <t>206.890mm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2228,17 +2228,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>65.255mm</t>
+          <t>91.850mm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>204.500mm</t>
+          <t>12.500mm</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2248,24 +2248,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>96.600mm</t>
+          <t>67.550mm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>200.000mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2275,24 +2275,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>R43</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>96.600mm</t>
+          <t>73.550mm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>197.000mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2302,24 +2302,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>R104</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>79.550mm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>153.500mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2329,24 +2329,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>R105</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>65.255mm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>155.000mm</t>
+          <t>218.890mm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2356,24 +2356,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>R106</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7.500mm</t>
+          <t>65.255mm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>145.500mm</t>
+          <t>213.390mm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2390,17 +2390,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>R107</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>90.170mm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>138.500mm</t>
+          <t>201.890mm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2417,17 +2417,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>R108</t>
+          <t>R43</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8.000mm</t>
+          <t>97.790mm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>166.500mm</t>
+          <t>201.890mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2437,24 +2437,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>R109</t>
+          <t>R44</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21.905mm</t>
+          <t>85.090mm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>169.500mm</t>
+          <t>194.390mm</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2471,17 +2471,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>R110</t>
+          <t>R104</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>11.500mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>173.000mm</t>
+          <t>153.500mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>R111</t>
+          <t>R105</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>178.500mm</t>
+          <t>155.000mm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2525,17 +2525,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>R112</t>
+          <t>R106</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>32.905mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>178.500mm</t>
+          <t>145.500mm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2552,17 +2552,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>R113</t>
+          <t>R107</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>178.500mm</t>
+          <t>138.500mm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2572,24 +2572,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>R114</t>
+          <t>R108</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>41.405mm</t>
+          <t>8.000mm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>169.500mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2606,12 +2606,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>R115</t>
+          <t>R109</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>50.810mm</t>
+          <t>21.905mm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2633,17 +2633,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>R116</t>
+          <t>R110</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>53.310mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>166.500mm</t>
+          <t>173.000mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2653,24 +2653,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>R117</t>
+          <t>R111</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>52.810mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>162.000mm</t>
+          <t>178.500mm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>R118</t>
+          <t>R112</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>42.810mm</t>
+          <t>32.905mm</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>153.500mm</t>
+          <t>178.500mm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2707,24 +2707,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>R119</t>
+          <t>R113</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>55.810mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>153.000mm</t>
+          <t>178.500mm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2734,24 +2734,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>R120</t>
+          <t>R114</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>41.405mm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>154.500mm</t>
+          <t>169.500mm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>R121</t>
+          <t>R115</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>50.810mm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>150.000mm</t>
+          <t>169.500mm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2795,17 +2795,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>R123</t>
+          <t>R116</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>85.350mm</t>
+          <t>53.310mm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>176.800mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2815,24 +2815,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>R150</t>
+          <t>R117</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>21.000mm</t>
+          <t>52.810mm</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>155.000mm</t>
+          <t>162.000mm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2849,17 +2849,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>R151</t>
+          <t>R118</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>25.500mm</t>
+          <t>42.810mm</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>152.500mm</t>
+          <t>153.500mm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2869,24 +2869,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>R204</t>
+          <t>R119</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>55.810mm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>99.500mm</t>
+          <t>153.000mm</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2896,24 +2896,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>R205</t>
+          <t>R120</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>101.000mm</t>
+          <t>154.500mm</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2930,17 +2930,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>R206</t>
+          <t>R121</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7.500mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>91.500mm</t>
+          <t>150.000mm</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2957,17 +2957,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>R207</t>
+          <t>R123</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>85.350mm</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>84.500mm</t>
+          <t>176.800mm</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2984,17 +2984,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>R208</t>
+          <t>R150</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8.000mm</t>
+          <t>21.000mm</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>112.500mm</t>
+          <t>155.000mm</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3004,24 +3004,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>R209</t>
+          <t>R151</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>21.905mm</t>
+          <t>25.500mm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>115.500mm</t>
+          <t>152.500mm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3038,17 +3038,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>R210</t>
+          <t>R152</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>11.500mm</t>
+          <t>52.705mm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>119.000mm</t>
+          <t>173.500mm</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3058,24 +3058,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>R211</t>
+          <t>R204</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>124.500mm</t>
+          <t>99.500mm</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3085,24 +3085,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>R212</t>
+          <t>R205</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>32.905mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>124.500mm</t>
+          <t>101.000mm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3112,24 +3112,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>R213</t>
+          <t>R206</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>124.500mm</t>
+          <t>91.500mm</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3146,17 +3146,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>R214</t>
+          <t>R207</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>41.405mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>115.500mm</t>
+          <t>84.500mm</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3166,24 +3166,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>R215</t>
+          <t>R208</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>50.810mm</t>
+          <t>8.000mm</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>115.500mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3200,17 +3200,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>R216</t>
+          <t>R209</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>53.310mm</t>
+          <t>21.905mm</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>112.500mm</t>
+          <t>115.500mm</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3227,17 +3227,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>R217</t>
+          <t>R210</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>52.810mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>108.000mm</t>
+          <t>119.000mm</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3247,24 +3247,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>R218</t>
+          <t>R211</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>42.810mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>99.500mm</t>
+          <t>124.500mm</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3281,17 +3281,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>R219</t>
+          <t>R212</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>55.810mm</t>
+          <t>32.905mm</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>99.000mm</t>
+          <t>124.500mm</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3301,24 +3301,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>R220</t>
+          <t>R213</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>100.500mm</t>
+          <t>124.500mm</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3328,24 +3328,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>R221</t>
+          <t>R214</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>41.405mm</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>96.000mm</t>
+          <t>115.500mm</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3362,17 +3362,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>R223</t>
+          <t>R215</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>85.350mm</t>
+          <t>50.810mm</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>122.800mm</t>
+          <t>115.500mm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3382,24 +3382,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>R250</t>
+          <t>R216</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>21.000mm</t>
+          <t>53.310mm</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>101.000mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3409,24 +3409,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>R251</t>
+          <t>R217</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>25.500mm</t>
+          <t>52.810mm</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>98.500mm</t>
+          <t>108.000mm</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>R304</t>
+          <t>R218</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>42.810mm</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>45.500mm</t>
+          <t>99.500mm</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3463,24 +3463,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>R305</t>
+          <t>R219</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>55.810mm</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>99.000mm</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3497,17 +3497,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>R306</t>
+          <t>R220</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7.500mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>37.500mm</t>
+          <t>100.500mm</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3517,24 +3517,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>R307</t>
+          <t>R221</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>30.500mm</t>
+          <t>96.000mm</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3544,24 +3544,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>R308</t>
+          <t>R223</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>8.000mm</t>
+          <t>85.350mm</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>122.800mm</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3571,24 +3571,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>R309</t>
+          <t>R250</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21.905mm</t>
+          <t>21.000mm</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>61.500mm</t>
+          <t>101.000mm</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3598,24 +3598,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>R310</t>
+          <t>R251</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>11.500mm</t>
+          <t>25.500mm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>98.500mm</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3625,24 +3625,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>R311</t>
+          <t>R252</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>52.705mm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>70.500mm</t>
+          <t>119.500mm</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3652,24 +3652,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>R312</t>
+          <t>R304</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>32.905mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>70.500mm</t>
+          <t>45.500mm</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3686,17 +3686,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>R313</t>
+          <t>R305</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>70.500mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>R314</t>
+          <t>R306</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>41.405mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>61.500mm</t>
+          <t>37.500mm</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3740,17 +3740,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>R315</t>
+          <t>R307</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>50.810mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>61.500mm</t>
+          <t>30.500mm</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3760,19 +3760,19 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>R316</t>
+          <t>R308</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>53.310mm</t>
+          <t>8.000mm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3794,17 +3794,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>R317</t>
+          <t>R309</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>52.810mm</t>
+          <t>21.905mm</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>54.000mm</t>
+          <t>61.500mm</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3814,24 +3814,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>R318</t>
+          <t>R310</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>42.810mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>45.500mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3841,24 +3841,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>R319</t>
+          <t>R311</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>55.810mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>45.000mm</t>
+          <t>70.500mm</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3875,17 +3875,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>R320</t>
+          <t>R312</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>32.905mm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>46.500mm</t>
+          <t>70.500mm</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3895,24 +3895,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>R321</t>
+          <t>R313</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>42.000mm</t>
+          <t>70.500mm</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3929,17 +3929,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>R323</t>
+          <t>R314</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>85.350mm</t>
+          <t>41.405mm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>68.800mm</t>
+          <t>61.500mm</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3949,24 +3949,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>R350</t>
+          <t>R315</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>21.000mm</t>
+          <t>50.810mm</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>61.500mm</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3976,24 +3976,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>R351</t>
+          <t>R316</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>25.500mm</t>
+          <t>53.310mm</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>44.500mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4010,17 +4010,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>R317</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>23.350mm</t>
+          <t>52.810mm</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>201.425mm</t>
+          <t>54.000mm</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4037,17 +4037,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>R318</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>88.350mm</t>
+          <t>42.810mm</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>13.500mm</t>
+          <t>45.500mm</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4064,17 +4064,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>R319</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>89.535mm</t>
+          <t>55.810mm</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>199.500mm</t>
+          <t>45.000mm</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4091,17 +4091,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>U102</t>
+          <t>R320</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>77.350mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>150.000mm</t>
+          <t>46.500mm</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4111,24 +4111,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>U109</t>
+          <t>R321</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>79.540mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>175.240mm</t>
+          <t>42.000mm</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4138,24 +4138,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>U202</t>
+          <t>R323</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>77.350mm</t>
+          <t>85.350mm</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>96.000mm</t>
+          <t>68.800mm</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4165,24 +4165,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>U209</t>
+          <t>R350</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>79.540mm</t>
+          <t>21.000mm</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>121.240mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4199,17 +4199,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>U302</t>
+          <t>R351</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>77.350mm</t>
+          <t>25.500mm</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>42.000mm</t>
+          <t>44.500mm</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4219,24 +4219,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>U309</t>
+          <t>R352</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>79.540mm</t>
+          <t>52.705mm</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>67.240mm</t>
+          <t>65.500mm</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4246,24 +4246,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>V101</t>
+          <t>RT1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>19.000mm</t>
+          <t>87.630mm</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>140.500mm</t>
+          <t>194.390mm</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4273,24 +4273,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>V102</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>49.810mm</t>
+          <t>23.350mm</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>148.500mm</t>
+          <t>210.315mm</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4307,17 +4307,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>V201</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>19.000mm</t>
+          <t>88.350mm</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>86.500mm</t>
+          <t>13.500mm</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4334,17 +4334,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>V202</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>49.810mm</t>
+          <t>86.995mm</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>94.500mm</t>
+          <t>208.390mm</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4361,17 +4361,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>V301</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>19.000mm</t>
+          <t>96.520mm</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>32.500mm</t>
+          <t>208.390mm</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4388,25 +4388,322 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
+          <t>U102</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>77.350mm</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>150.000mm</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>U109</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>79.540mm</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>175.240mm</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>U202</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>77.350mm</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>96.000mm</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>U209</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>79.540mm</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>121.240mm</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>U302</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>77.350mm</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>42.000mm</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>U309</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>79.540mm</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>67.240mm</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>V101</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>19.000mm</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>140.500mm</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>V102</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>49.810mm</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>148.500mm</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>V201</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>19.000mm</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>86.500mm</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>V202</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>49.810mm</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>94.500mm</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>V301</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>19.000mm</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>32.500mm</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
           <t>V302</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>49.810mm</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>40.500mm</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/hardware/variante_3ch/jlcpcb/CPL_JLCPCB.xlsx
+++ b/hardware/variante_3ch/jlcpcb/CPL_JLCPCB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E159"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C60</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>14.605mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>142.000mm</t>
+          <t>195.315mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -635,17 +635,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>166.500mm</t>
+          <t>142.000mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,24 +655,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C107</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18.405mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>174.000mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,24 +682,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C109</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>58.310mm</t>
+          <t>18.405mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>166.500mm</t>
+          <t>174.000mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -716,17 +716,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C111</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>46.040mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>174.000mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -743,17 +743,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C121</t>
+          <t>C111</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>46.040mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>146.000mm</t>
+          <t>174.000mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -763,24 +763,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C150</t>
+          <t>C121</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>152.500mm</t>
+          <t>146.000mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -797,17 +797,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C152</t>
+          <t>C150</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50.165mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>173.500mm</t>
+          <t>152.500mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -824,17 +824,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C204</t>
+          <t>C152</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>50.165mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>88.000mm</t>
+          <t>173.500mm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -844,24 +844,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C206</t>
+          <t>C204</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>112.500mm</t>
+          <t>88.000mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -871,24 +871,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C207</t>
+          <t>C206</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18.405mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>120.000mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -898,24 +898,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C209</t>
+          <t>C207</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>58.310mm</t>
+          <t>18.405mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>112.500mm</t>
+          <t>120.000mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -932,17 +932,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C211</t>
+          <t>C209</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>46.040mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>120.000mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -959,17 +959,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C221</t>
+          <t>C211</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>46.040mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>92.000mm</t>
+          <t>120.000mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -979,24 +979,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C250</t>
+          <t>C221</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>98.500mm</t>
+          <t>92.000mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1013,17 +1013,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C252</t>
+          <t>C250</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>50.165mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>119.500mm</t>
+          <t>98.500mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1040,17 +1040,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C304</t>
+          <t>C252</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>50.165mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>34.000mm</t>
+          <t>119.500mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1060,24 +1060,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C306</t>
+          <t>C304</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>34.000mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1087,24 +1087,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C307</t>
+          <t>C306</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18.405mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>66.000mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C309</t>
+          <t>C307</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>58.310mm</t>
+          <t>18.405mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>66.000mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1148,17 +1148,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C311</t>
+          <t>C309</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>46.040mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>66.000mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1175,17 +1175,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C321</t>
+          <t>C311</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>46.040mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>38.000mm</t>
+          <t>66.000mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1195,24 +1195,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C350</t>
+          <t>C321</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>44.500mm</t>
+          <t>38.000mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1229,17 +1229,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C352</t>
+          <t>C350</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>50.165mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>65.500mm</t>
+          <t>44.500mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1256,17 +1256,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CF4</t>
+          <t>C352</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>75.890mm</t>
+          <t>50.165mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>215.890mm</t>
+          <t>65.500mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CF7</t>
+          <t>CF4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>205.890mm</t>
+          <t>215.890mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1310,17 +1310,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CF8</t>
+          <t>CF7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20.350mm</t>
+          <t>75.890mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>203.890mm</t>
+          <t>205.890mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1330,19 +1330,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CF9</t>
+          <t>CF8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>26.350mm</t>
+          <t>20.350mm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,17 +1364,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CF11</t>
+          <t>CF9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>88.350mm</t>
+          <t>26.350mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>18.500mm</t>
+          <t>203.890mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1391,17 +1391,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CF12</t>
+          <t>CF11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>86.360mm</t>
+          <t>88.350mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>201.890mm</t>
+          <t>18.500mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1418,12 +1418,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CF13</t>
+          <t>CF12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93.980mm</t>
+          <t>86.360mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,17 +1445,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CF101</t>
+          <t>CF13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>29.405mm</t>
+          <t>93.980mm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>181.500mm</t>
+          <t>201.890mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1472,17 +1472,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CF102</t>
+          <t>CF101</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>58.310mm</t>
+          <t>29.405mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>179.000mm</t>
+          <t>181.500mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1499,17 +1499,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CF105</t>
+          <t>CF102</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>82.350mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>155.000mm</t>
+          <t>179.000mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1526,17 +1526,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CF106</t>
+          <t>CF105</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>71.850mm</t>
+          <t>82.350mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>150.000mm</t>
+          <t>155.000mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CF110</t>
+          <t>CF106</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>79.350mm</t>
+          <t>71.850mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>180.000mm</t>
+          <t>150.000mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CF201</t>
+          <t>CF110</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>29.405mm</t>
+          <t>79.350mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>127.500mm</t>
+          <t>180.000mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1607,17 +1607,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CF202</t>
+          <t>CF201</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>58.310mm</t>
+          <t>29.405mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>125.000mm</t>
+          <t>127.500mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1634,17 +1634,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CF205</t>
+          <t>CF202</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>82.350mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>101.000mm</t>
+          <t>125.000mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1661,17 +1661,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CF206</t>
+          <t>CF205</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>71.850mm</t>
+          <t>82.350mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>96.000mm</t>
+          <t>101.000mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1681,24 +1681,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CF210</t>
+          <t>CF206</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>79.350mm</t>
+          <t>71.850mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>126.000mm</t>
+          <t>96.000mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1708,24 +1708,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CF301</t>
+          <t>CF210</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>29.405mm</t>
+          <t>79.350mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>73.500mm</t>
+          <t>126.000mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1742,17 +1742,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CF302</t>
+          <t>CF301</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>58.310mm</t>
+          <t>29.405mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>71.000mm</t>
+          <t>73.500mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1769,17 +1769,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CF305</t>
+          <t>CF302</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>82.350mm</t>
+          <t>58.310mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>71.000mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1796,17 +1796,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CF306</t>
+          <t>CF305</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>71.850mm</t>
+          <t>82.350mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>42.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CF310</t>
+          <t>CF306</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>79.350mm</t>
+          <t>71.850mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>72.000mm</t>
+          <t>42.000mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1843,24 +1843,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>CF310</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>79.350mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>144.000mm</t>
+          <t>72.000mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1870,24 +1870,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D203</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>14.605mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>90.000mm</t>
+          <t>206.890mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1904,17 +1904,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>D303</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>15.240mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>191.890mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1924,24 +1924,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>39.255mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>212.890mm</t>
+          <t>144.000mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1958,17 +1958,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Q101</t>
+          <t>D203</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>172.117mm</t>
+          <t>90.000mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1978,24 +1978,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Q102</t>
+          <t>D303</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>173.383mm</t>
+          <t>36.000mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2005,24 +2005,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Q201</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>14.605mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>118.117mm</t>
+          <t>214.390mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2032,24 +2032,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Q202</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>3.400mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>119.383mm</t>
+          <t>206.890mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Q301</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>39.255mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>64.117mm</t>
+          <t>212.890mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2086,24 +2086,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Q302</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>14.605mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>65.383mm</t>
+          <t>199.377mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2113,24 +2113,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Q101</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>57.755mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>206.890mm</t>
+          <t>172.117mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2140,24 +2140,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Q102</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>54.755mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>206.890mm</t>
+          <t>173.383mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2167,24 +2167,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Q201</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>47.255mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>210.890mm</t>
+          <t>118.117mm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2201,17 +2201,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>Q202</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>51.755mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>206.890mm</t>
+          <t>119.383mm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2221,24 +2221,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>Q301</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>91.850mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>12.500mm</t>
+          <t>64.117mm</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2248,24 +2248,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>Q302</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>67.550mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>65.383mm</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2275,24 +2275,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>73.550mm</t>
+          <t>57.755mm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>206.890mm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2302,24 +2302,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>79.550mm</t>
+          <t>54.755mm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>206.890mm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2329,24 +2329,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>65.255mm</t>
+          <t>47.255mm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>218.890mm</t>
+          <t>210.890mm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2356,24 +2356,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>65.255mm</t>
+          <t>51.755mm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>213.390mm</t>
+          <t>206.890mm</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2390,17 +2390,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>90.170mm</t>
+          <t>91.850mm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>201.890mm</t>
+          <t>12.500mm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2410,24 +2410,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>R43</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>97.790mm</t>
+          <t>67.550mm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>201.890mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2437,24 +2437,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>R44</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>85.090mm</t>
+          <t>73.550mm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>194.390mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2464,24 +2464,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>R104</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>79.550mm</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>153.500mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>R105</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>65.255mm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>155.000mm</t>
+          <t>218.890mm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>R106</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7.500mm</t>
+          <t>65.255mm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>145.500mm</t>
+          <t>213.390mm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2552,17 +2552,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>R107</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>90.170mm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>138.500mm</t>
+          <t>201.890mm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2579,17 +2579,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>R108</t>
+          <t>R43</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8.000mm</t>
+          <t>97.790mm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>166.500mm</t>
+          <t>201.890mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2599,24 +2599,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>R109</t>
+          <t>R44</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21.905mm</t>
+          <t>85.090mm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>169.500mm</t>
+          <t>194.390mm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2633,17 +2633,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>R110</t>
+          <t>R60</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11.500mm</t>
+          <t>10.795mm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>173.000mm</t>
+          <t>207.890mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2653,24 +2653,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>R111</t>
+          <t>R61</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>10.795mm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>178.500mm</t>
+          <t>205.890mm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>R112</t>
+          <t>R62</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>32.905mm</t>
+          <t>11.430mm</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>178.500mm</t>
+          <t>198.490mm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2714,17 +2714,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>R113</t>
+          <t>R63</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>11.430mm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>178.500mm</t>
+          <t>191.890mm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2734,24 +2734,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>R114</t>
+          <t>R104</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>41.405mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>169.500mm</t>
+          <t>153.500mm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2768,17 +2768,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>R115</t>
+          <t>R105</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>50.810mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>169.500mm</t>
+          <t>155.000mm</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2788,24 +2788,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>R116</t>
+          <t>R106</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>53.310mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>166.500mm</t>
+          <t>145.500mm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2822,17 +2822,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>R117</t>
+          <t>R107</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>52.810mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>162.000mm</t>
+          <t>138.500mm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2849,17 +2849,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>R118</t>
+          <t>R108</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>42.810mm</t>
+          <t>8.000mm</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>153.500mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2869,24 +2869,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>R119</t>
+          <t>R109</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>55.810mm</t>
+          <t>21.905mm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>153.000mm</t>
+          <t>169.500mm</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2896,24 +2896,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>R120</t>
+          <t>R110</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>154.500mm</t>
+          <t>173.000mm</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2923,24 +2923,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>R121</t>
+          <t>R111</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>150.000mm</t>
+          <t>178.500mm</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2950,24 +2950,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>R123</t>
+          <t>R112</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>85.350mm</t>
+          <t>32.905mm</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>176.800mm</t>
+          <t>178.500mm</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2977,24 +2977,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>R150</t>
+          <t>R113</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>21.000mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>155.000mm</t>
+          <t>178.500mm</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3004,24 +3004,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>R151</t>
+          <t>R114</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>25.500mm</t>
+          <t>41.405mm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>152.500mm</t>
+          <t>169.500mm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3038,17 +3038,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>R152</t>
+          <t>R115</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>52.705mm</t>
+          <t>50.810mm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>173.500mm</t>
+          <t>169.500mm</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3065,17 +3065,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>R204</t>
+          <t>R116</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>53.310mm</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>99.500mm</t>
+          <t>166.500mm</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3092,17 +3092,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>R205</t>
+          <t>R117</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>52.810mm</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>101.000mm</t>
+          <t>162.000mm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3119,17 +3119,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>R206</t>
+          <t>R118</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7.500mm</t>
+          <t>42.810mm</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>91.500mm</t>
+          <t>153.500mm</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3139,24 +3139,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>R207</t>
+          <t>R119</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>55.810mm</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>84.500mm</t>
+          <t>153.000mm</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3173,17 +3173,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>R208</t>
+          <t>R120</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>8.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>112.500mm</t>
+          <t>154.500mm</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3193,24 +3193,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>R209</t>
+          <t>R121</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>21.905mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>115.500mm</t>
+          <t>150.000mm</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3227,17 +3227,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>R210</t>
+          <t>R123</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>11.500mm</t>
+          <t>85.350mm</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>119.000mm</t>
+          <t>176.800mm</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3247,24 +3247,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>R211</t>
+          <t>R150</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>21.000mm</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>124.500mm</t>
+          <t>155.000mm</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3281,17 +3281,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>R212</t>
+          <t>R151</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>32.905mm</t>
+          <t>25.500mm</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>124.500mm</t>
+          <t>152.500mm</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3308,17 +3308,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>R213</t>
+          <t>R152</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>52.705mm</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>124.500mm</t>
+          <t>173.500mm</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3335,17 +3335,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>R214</t>
+          <t>R204</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>41.405mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>115.500mm</t>
+          <t>99.500mm</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3362,17 +3362,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>R215</t>
+          <t>R205</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>50.810mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>115.500mm</t>
+          <t>101.000mm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3382,24 +3382,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>R216</t>
+          <t>R206</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>53.310mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>112.500mm</t>
+          <t>91.500mm</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3416,17 +3416,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>R217</t>
+          <t>R207</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>52.810mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>108.000mm</t>
+          <t>84.500mm</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3443,17 +3443,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>R218</t>
+          <t>R208</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>42.810mm</t>
+          <t>8.000mm</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>99.500mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3463,24 +3463,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>R219</t>
+          <t>R209</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>55.810mm</t>
+          <t>21.905mm</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>99.000mm</t>
+          <t>115.500mm</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3490,24 +3490,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>R220</t>
+          <t>R210</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>100.500mm</t>
+          <t>119.000mm</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3517,24 +3517,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>R221</t>
+          <t>R211</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>96.000mm</t>
+          <t>124.500mm</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3544,24 +3544,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>R223</t>
+          <t>R212</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>85.350mm</t>
+          <t>32.905mm</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>122.800mm</t>
+          <t>124.500mm</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3571,24 +3571,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>R250</t>
+          <t>R213</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21.000mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>101.000mm</t>
+          <t>124.500mm</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3598,24 +3598,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>R251</t>
+          <t>R214</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>25.500mm</t>
+          <t>41.405mm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>98.500mm</t>
+          <t>115.500mm</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3632,17 +3632,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>R252</t>
+          <t>R215</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>52.705mm</t>
+          <t>50.810mm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>119.500mm</t>
+          <t>115.500mm</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3659,17 +3659,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>R304</t>
+          <t>R216</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>53.310mm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>45.500mm</t>
+          <t>112.500mm</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3686,17 +3686,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>R305</t>
+          <t>R217</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>13.000mm</t>
+          <t>52.810mm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>108.000mm</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>R306</t>
+          <t>R218</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7.500mm</t>
+          <t>42.810mm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>37.500mm</t>
+          <t>99.500mm</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3733,24 +3733,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>R307</t>
+          <t>R219</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>12.000mm</t>
+          <t>55.810mm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>30.500mm</t>
+          <t>99.000mm</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3767,17 +3767,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>R308</t>
+          <t>R220</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>8.000mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>100.500mm</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3787,24 +3787,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>R309</t>
+          <t>R221</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21.905mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>61.500mm</t>
+          <t>96.000mm</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3821,17 +3821,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>R310</t>
+          <t>R223</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>11.500mm</t>
+          <t>85.350mm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>65.000mm</t>
+          <t>122.800mm</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3841,24 +3841,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>R311</t>
+          <t>R250</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>26.905mm</t>
+          <t>21.000mm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>70.500mm</t>
+          <t>101.000mm</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3875,17 +3875,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>R312</t>
+          <t>R251</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>32.905mm</t>
+          <t>25.500mm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>70.500mm</t>
+          <t>98.500mm</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3902,17 +3902,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>R313</t>
+          <t>R252</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>37.405mm</t>
+          <t>52.705mm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>70.500mm</t>
+          <t>119.500mm</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3929,17 +3929,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>R314</t>
+          <t>R304</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>41.405mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>61.500mm</t>
+          <t>45.500mm</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3956,17 +3956,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>R315</t>
+          <t>R305</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>50.810mm</t>
+          <t>13.000mm</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>61.500mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3976,24 +3976,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>R316</t>
+          <t>R306</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>53.310mm</t>
+          <t>7.500mm</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>58.500mm</t>
+          <t>37.500mm</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4010,17 +4010,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>R317</t>
+          <t>R307</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>52.810mm</t>
+          <t>12.000mm</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>54.000mm</t>
+          <t>30.500mm</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4037,17 +4037,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>R318</t>
+          <t>R308</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>42.810mm</t>
+          <t>8.000mm</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>45.500mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4057,24 +4057,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>R319</t>
+          <t>R309</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>55.810mm</t>
+          <t>21.905mm</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>45.000mm</t>
+          <t>61.500mm</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4084,24 +4084,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>R320</t>
+          <t>R310</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>71.350mm</t>
+          <t>11.500mm</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>46.500mm</t>
+          <t>65.000mm</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4111,24 +4111,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>R321</t>
+          <t>R311</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>85.850mm</t>
+          <t>26.905mm</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>42.000mm</t>
+          <t>70.500mm</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4138,24 +4138,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>R323</t>
+          <t>R312</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>85.350mm</t>
+          <t>32.905mm</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>68.800mm</t>
+          <t>70.500mm</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4165,24 +4165,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>R350</t>
+          <t>R313</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>21.000mm</t>
+          <t>37.405mm</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>47.000mm</t>
+          <t>70.500mm</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4192,24 +4192,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>R351</t>
+          <t>R314</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>25.500mm</t>
+          <t>41.405mm</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>44.500mm</t>
+          <t>61.500mm</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4226,17 +4226,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>R352</t>
+          <t>R315</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>52.705mm</t>
+          <t>50.810mm</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>65.500mm</t>
+          <t>61.500mm</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4253,17 +4253,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RT1</t>
+          <t>R316</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>87.630mm</t>
+          <t>53.310mm</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>194.390mm</t>
+          <t>58.500mm</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4280,17 +4280,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>R317</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>23.350mm</t>
+          <t>52.810mm</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>210.315mm</t>
+          <t>54.000mm</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4307,17 +4307,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>R318</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>88.350mm</t>
+          <t>42.810mm</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>13.500mm</t>
+          <t>45.500mm</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4334,17 +4334,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>R319</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>86.995mm</t>
+          <t>55.810mm</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>208.390mm</t>
+          <t>45.000mm</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4361,17 +4361,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>R320</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>96.520mm</t>
+          <t>71.350mm</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>208.390mm</t>
+          <t>46.500mm</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4388,17 +4388,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>U102</t>
+          <t>R321</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>77.350mm</t>
+          <t>85.850mm</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>150.000mm</t>
+          <t>42.000mm</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4408,24 +4408,24 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>U109</t>
+          <t>R323</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>79.540mm</t>
+          <t>85.350mm</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>175.240mm</t>
+          <t>68.800mm</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4442,17 +4442,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>U202</t>
+          <t>R350</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>77.350mm</t>
+          <t>21.000mm</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>96.000mm</t>
+          <t>47.000mm</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4462,24 +4462,24 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>U209</t>
+          <t>R351</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>79.540mm</t>
+          <t>25.500mm</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>121.240mm</t>
+          <t>44.500mm</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4489,24 +4489,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>U302</t>
+          <t>R352</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>77.350mm</t>
+          <t>52.705mm</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>42.000mm</t>
+          <t>65.500mm</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4516,24 +4516,24 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>U309</t>
+          <t>RT1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>79.540mm</t>
+          <t>87.630mm</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>67.240mm</t>
+          <t>194.390mm</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4543,24 +4543,24 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>V101</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>19.000mm</t>
+          <t>23.350mm</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>140.500mm</t>
+          <t>210.315mm</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4577,17 +4577,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>V102</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>49.810mm</t>
+          <t>88.350mm</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>148.500mm</t>
+          <t>13.500mm</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4604,17 +4604,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>V201</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>19.000mm</t>
+          <t>86.995mm</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>86.500mm</t>
+          <t>208.390mm</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4631,17 +4631,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>V202</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>49.810mm</t>
+          <t>96.520mm</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>94.500mm</t>
+          <t>208.390mm</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4658,17 +4658,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>V301</t>
+          <t>U102</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>19.000mm</t>
+          <t>77.350mm</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>32.500mm</t>
+          <t>150.000mm</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4678,32 +4678,302 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>U109</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>79.540mm</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>175.240mm</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>U202</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>77.350mm</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>96.000mm</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>U209</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>79.540mm</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>121.240mm</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>U302</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>77.350mm</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>42.000mm</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>U309</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>79.540mm</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>67.240mm</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>V101</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>19.000mm</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>140.500mm</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>V102</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>49.810mm</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>148.500mm</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>V201</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>19.000mm</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>86.500mm</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>V202</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>49.810mm</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>94.500mm</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>V301</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>19.000mm</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>32.500mm</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
           <t>V302</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>49.810mm</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>40.500mm</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
         <is>
           <t>0</t>
         </is>
